--- a/Documentos Base/Sprint 4 documentacion/Sprint_04_Backlog_ICARO.xlsx
+++ b/Documentos Base/Sprint 4 documentacion/Sprint_04_Backlog_ICARO.xlsx
@@ -8,12 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Desktop\Sistema_Gestion_Integral_Constructora\Documentos Base\Sprint 4 documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B1BDBB2-8527-4E7A-AB48-38A0A40C8A8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3043EBB9-4AC4-4DEF-83F9-D326ACE05761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="1455" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Backlog Sprint 04" sheetId="1" r:id="rId1"/>
+    <sheet name="Backlog Sprint 04" sheetId="4" r:id="rId1"/>
     <sheet name="Resumen Velocidad" sheetId="2" r:id="rId2"/>
     <sheet name="Glosario" sheetId="3" r:id="rId3"/>
   </sheets>
@@ -22,10 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="121">
-  <si>
-    <t>SPRINT BACKLOG — Sprint 04: Módulo de Requerimientos de Compra</t>
-  </si>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="150">
   <si>
     <t>ICARO CONSTRUCTORES BMGM S.A.S.</t>
   </si>
@@ -33,21 +30,12 @@
     <t>Proyecto:</t>
   </si>
   <si>
-    <t>ICARO CONSTRUCTORES BMGM S.A.S. — Sistema de Gestión Integral de Obra</t>
-  </si>
-  <si>
     <t>Fecha de inicio:</t>
   </si>
   <si>
-    <t>2026-04-04</t>
-  </si>
-  <si>
     <t>Objetivo:</t>
   </si>
   <si>
-    <t>Implementar el módulo de Requerimientos de Compra con CRUD completo, flujo de aprobación/rechazo con RBAC, y formalizar el endpoint de reactivación de materiales (HT-09).</t>
-  </si>
-  <si>
     <t>Vel. estimada (SP):</t>
   </si>
   <si>
@@ -87,18 +75,9 @@
     <t>Alta</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
     <t>HU-13</t>
   </si>
   <si>
-    <t>Aprobar requerimiento de compra (estado APROBADO)</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
     <t>HU-14</t>
   </si>
   <si>
@@ -120,9 +99,6 @@
     <t>HT-09</t>
   </si>
   <si>
-    <t>Formalizar endpoint de reactivación de materiales (PUT /materiales/:id activo:true)</t>
-  </si>
-  <si>
     <t>HT</t>
   </si>
   <si>
@@ -237,9 +213,6 @@
     <t>compras_requerimientos.test.js</t>
   </si>
   <si>
-    <t>Compromisos Sprint 03 §8.3 cum.</t>
-  </si>
-  <si>
     <t>5/5</t>
   </si>
   <si>
@@ -385,13 +358,127 @@
   </si>
   <si>
     <t>Documento de resultados de pruebas del sprint</t>
+  </si>
+  <si>
+    <t>Compromisos Sprint 03 8.3 cum.</t>
+  </si>
+  <si>
+    <t>SPRINT BACKLOG — Sprint 03: Catalogo de Materiales, Gestion de Bodega e Inventario</t>
+  </si>
+  <si>
+    <t>ICARO CONSTRUCTORES BMGM S.A.S.  |  Sistema de Gestion Integral de Obra</t>
+  </si>
+  <si>
+    <t>Sprint N°:</t>
+  </si>
+  <si>
+    <t>Fecha de cierre:</t>
+  </si>
+  <si>
+    <t>Scrum Master:</t>
+  </si>
+  <si>
+    <t>Ivan Santiago Pulgar Leon</t>
+  </si>
+  <si>
+    <t>Estado:</t>
+  </si>
+  <si>
+    <t>Cerrado – 100% completado</t>
+  </si>
+  <si>
+    <t>SP Real</t>
+  </si>
+  <si>
+    <t>Responsable</t>
+  </si>
+  <si>
+    <t>Estado</t>
+  </si>
+  <si>
+    <t>Observaciones</t>
+  </si>
+  <si>
+    <t>Evidencia / Ref.</t>
+  </si>
+  <si>
+    <t>Isaac Sebastian Castro Muesmueran / Ivan Santiago Pulgar Leon</t>
+  </si>
+  <si>
+    <t>Completado</t>
+  </si>
+  <si>
+    <t>Criterios de Aceptación</t>
+  </si>
+  <si>
+    <t>El sistema permite crear requerimientos de compra asociados a un proyecto. El requerimiento debe incluir materiales, cantidades y justificación. Solo los roles autorizados pueden crear requerimientos. POST /api/v1/requerimientos retorna 401 si no existe token. POST /api/v1/requerimientos retorna 403 si el rol no tiene permiso de creación. Si el body está vacío o faltan campos obligatorios, retorna 400 o error controlado según disponibilidad de BD. El requerimiento se registra inicialmente en estado En Revisión o equivalente funcional.</t>
+  </si>
+  <si>
+    <t>Completado. Se validó protección de ruta, control de roles y validación de campos obligatorios. La creación queda asociada al flujo posterior de aprobación o rechazo.</t>
+  </si>
+  <si>
+    <t>backend/src/routes/requerimientos.routes.js, backend/src/controllers/requerimientos.controller.js, backend/src/services/requerimientos.service.js, backend/tests/compras_requerimientos.test.js</t>
+  </si>
+  <si>
+    <t>Aprobar requerimiento de compra</t>
+  </si>
+  <si>
+    <t>El sistema permite aprobar un requerimiento mediante PATCH /api/v1/requerimientos//aprobar. La ruta está protegida por autenticación. Si no existe token, retorna 401. Si el rol no está autorizado, retorna 403. Un rol autorizado, como Admin, pasa RBAC y no recibe 403. Si el requerimiento no existe o la BD no está disponible, puede retornar 404 o 500 sin invalidar la prueba de permisos.</t>
+  </si>
+  <si>
+    <t>Completado. El flujo de aprobación quedó protegido por RBAC y preparado para cambiar el estado del requerimiento a APROBADO cuando exista el registro en BD.</t>
+  </si>
+  <si>
+    <t>backend/src/routes/requerimientos.routes.js, backend/src/controllers/requerimientos.controller.js, backend/src/services/requerimientos.service.js, compras_requerimientos.test.js – Tests 9, 10 y 11</t>
+  </si>
+  <si>
+    <t>El sistema permite rechazar un requerimiento mediante PATCH /api/v1/requerimientos//rechazar. La ruta está protegida por autenticación. Sin token retorna 401. Con rol no autorizado retorna 403. El rechazo exige justificación u observación obligatoria. Si se intenta rechazar sin justificación, retorna HTTP 400 con mensaje de validación.</t>
+  </si>
+  <si>
+    <t>Completado. Se validó la regla de negocio que impide rechazar requerimientos sin justificación, manteniendo trazabilidad funcional del motivo de rechazo.</t>
+  </si>
+  <si>
+    <t>backend/src/routes/requerimientos.routes.js, backend/src/controllers/requerimientos.controller.js, backend/src/services/requerimientos.service.js, compras_requerimientos.test.js – Tests 12, 13 y 14</t>
+  </si>
+  <si>
+    <t>GET /api/v1/requerimientos permite consultar requerimientos registrados. La ruta está protegida por autenticación. Sin token retorna 401. Roles con permiso de lectura, como Residente y Admin, pasan RBAC y no reciben 401 ni 403. El endpoint queda preparado para filtros por proyecto, estado, solicitante o fecha, según disponibilidad de datos y parámetros implementados.</t>
+  </si>
+  <si>
+    <t>Completado. La consulta de requerimientos fue validada a nivel de autenticación y RBAC. La disponibilidad de resultados depende de la existencia de registros y conexión a BD.</t>
+  </si>
+  <si>
+    <t>backend/src/routes/requerimientos.routes.js, backend/src/controllers/requerimientos.controller.js, backend/src/services/requerimientos.service.js, compras_requerimientos.test.js – Tests 4, 5 y 6</t>
+  </si>
+  <si>
+    <t>Formalizar endpoint de reactivación de materiales</t>
+  </si>
+  <si>
+    <t>Se formaliza PUT /api/v1/materiales/ como endpoint para actualización o reactivación de materiales. La ruta está protegida por autenticación. Sin token retorna 401. Con rol Residente retorna 403. Con Admin pasa RBAC y no recibe 403. Si se envía activo, el sistema reactiva el material dado de baja cuando la BD está disponible.</t>
+  </si>
+  <si>
+    <t>Completado. El endpoint complementa el soft-delete implementado en el Sprint 03, permitiendo revertir una baja lógica sin eliminar ni recrear materiales del catálogo.</t>
+  </si>
+  <si>
+    <t>backend/src/routes/materiales.routes.js, backend/src/controllers/materiales.controller.js, backend/src/services/materiales.service.js, compras_requerimientos.test.js – Tests 15, 16, 17 y 18</t>
+  </si>
+  <si>
+    <t>18 casos de prueba automatizados en compras_requerimientos.test.js. Grupo 1: creación, consulta y eliminación de requerimientos con autenticación, RBAC y validación de campos. Grupo 2: aprobación y rechazo de requerimientos, incluyendo protección sin token, denegación por rol y justificación obligatoria para rechazo. Grupo 3: actualización/reactivación de materiales mediante PUT /materiales/, validando autenticación, RBAC y reactivación con activo. Todos los casos deben finalizar en PASS.</t>
+  </si>
+  <si>
+    <t>18/18 pruebas PASS. La suite valida seguridad, permisos por rol, reglas mínimas de negocio y comportamiento esperado ante ausencia de BD o registros inexistentes.</t>
+  </si>
+  <si>
+    <t>backend/tests/compras_requerimientos.test.js</t>
+  </si>
+  <si>
+    <t>Implementar el módulo de Requerimientos de Compra con CRUD completo, registro de líneas de detalle, consulta por proyecto, filtros operativos, flujo de aprobación y rechazo con control RBAC, validación de justificación obligatoria para rechazos y formalización del endpoint de reactivación de materiales dados de baja. Adicionalmente, ampliar la cobertura de pruebas automatizadas sobre requerimientos de compra, aprobación/rechazo y reactivación de materiales</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -403,11 +490,6 @@
       <b/>
       <sz val="13"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF595959"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -445,8 +527,23 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <i/>
+      <sz val="9"/>
+      <color rgb="FF595959"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <name val="Calibri"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -478,8 +575,13 @@
         <fgColor rgb="FF2E75B6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -502,61 +604,130 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFBFBFBF"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFBFBFBF"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFBFBFBF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFBFBFBF"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="14" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -858,249 +1029,439 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{023A4DB3-4E78-4D63-B506-FBDBD8DF719F}">
+  <dimension ref="A1:L14"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="105.5703125" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="5" max="5" width="12" customWidth="1"/>
-    <col min="6" max="6" width="10" customWidth="1"/>
+    <col min="2" max="2" width="34.5703125" customWidth="1"/>
+    <col min="6" max="6" width="9.5703125" customWidth="1"/>
+    <col min="8" max="8" width="20.7109375" customWidth="1"/>
+    <col min="10" max="10" width="48.42578125" customWidth="1"/>
+    <col min="11" max="11" width="25.85546875" customWidth="1"/>
+    <col min="12" max="12" width="44.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:12" ht="17.25" x14ac:dyDescent="0.25">
+      <c r="A1" s="10" t="s">
+        <v>113</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+      <c r="G1" s="7"/>
+      <c r="H1" s="7"/>
+      <c r="I1" s="7"/>
+      <c r="J1" s="7"/>
+      <c r="K1" s="7"/>
+      <c r="L1" s="7"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A2" s="11" t="s">
+        <v>114</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
+      <c r="I2" s="7"/>
+      <c r="J2" s="7"/>
+      <c r="K2" s="7"/>
+      <c r="L2" s="7"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="13" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-      <c r="E1" s="12"/>
-      <c r="F1" s="12"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="13" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
+      <c r="C3" s="14"/>
+      <c r="D3" s="14"/>
+      <c r="E3" s="14"/>
+      <c r="F3" s="15"/>
+      <c r="G3" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="H3" s="29">
+        <v>4</v>
+      </c>
+      <c r="I3" s="30"/>
+      <c r="J3" s="30"/>
+      <c r="K3" s="30"/>
+      <c r="L3" s="31"/>
+    </row>
+    <row r="4" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B4" s="16">
+        <v>46116</v>
+      </c>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="18"/>
+      <c r="G4" s="12" t="s">
+        <v>116</v>
+      </c>
+      <c r="H4" s="16">
+        <v>46150</v>
+      </c>
+      <c r="I4" s="17"/>
+      <c r="J4" s="17"/>
+      <c r="K4" s="17"/>
+      <c r="L4" s="18"/>
+    </row>
+    <row r="5" spans="1:12" ht="95.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="12" t="s">
         <v>3</v>
       </c>
-      <c r="C3" s="12"/>
-      <c r="D3" s="12"/>
-      <c r="E3" s="12"/>
-      <c r="F3" s="12"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
+      <c r="B5" s="13" t="s">
+        <v>149</v>
+      </c>
+      <c r="C5" s="14"/>
+      <c r="D5" s="14"/>
+      <c r="E5" s="14"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="H5" s="13" t="s">
+        <v>118</v>
+      </c>
+      <c r="I5" s="14"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="15"/>
+    </row>
+    <row r="6" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+      <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="11" t="s">
+      <c r="B6" s="29">
+        <v>22</v>
+      </c>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="12" t="s">
+        <v>119</v>
+      </c>
+      <c r="H6" s="13" t="s">
+        <v>120</v>
+      </c>
+      <c r="I6" s="14"/>
+      <c r="J6" s="14"/>
+      <c r="K6" s="14"/>
+      <c r="L6" s="15"/>
+    </row>
+    <row r="7" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="G7" s="19" t="s">
+        <v>121</v>
+      </c>
+      <c r="H7" s="19" t="s">
+        <v>122</v>
+      </c>
+      <c r="I7" s="19" t="s">
+        <v>123</v>
+      </c>
+      <c r="J7" s="19" t="s">
+        <v>128</v>
+      </c>
+      <c r="K7" s="19" t="s">
+        <v>124</v>
+      </c>
+      <c r="L7" s="19" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="126.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="20" t="s">
+        <v>12</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="E8" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" s="20">
         <v>5</v>
       </c>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12"/>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12"/>
-    </row>
-    <row r="5" spans="1:6" ht="35.1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B5" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-    </row>
-    <row r="6" spans="1:6" ht="24" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-    </row>
-    <row r="7" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E7" s="3" t="s">
+      <c r="G8" s="20">
+        <v>5</v>
+      </c>
+      <c r="H8" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="I8" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="J8" s="21" t="s">
+        <v>129</v>
+      </c>
+      <c r="K8" s="21" t="s">
+        <v>130</v>
+      </c>
+      <c r="L8" s="21" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9" s="24" t="s">
+        <v>132</v>
+      </c>
+      <c r="C9" s="23" t="s">
         <v>14</v>
       </c>
-      <c r="F7" s="3" t="s">
+      <c r="D9" s="24" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="1:6" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="E9" s="23" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C8" s="4" t="s">
+      <c r="F9" s="23">
+        <v>3</v>
+      </c>
+      <c r="G9" s="23">
+        <v>3</v>
+      </c>
+      <c r="H9" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="I9" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="J9" s="24" t="s">
+        <v>133</v>
+      </c>
+      <c r="K9" s="24" t="s">
+        <v>134</v>
+      </c>
+      <c r="L9" s="24" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="120.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="B10" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="E8" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F8" s="4" t="s">
+      <c r="C10" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="D10" s="21" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="20">
+        <v>2</v>
+      </c>
+      <c r="G10" s="20">
+        <v>2</v>
+      </c>
+      <c r="H10" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="I10" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="J10" s="21" t="s">
+        <v>136</v>
+      </c>
+      <c r="K10" s="21" t="s">
+        <v>137</v>
+      </c>
+      <c r="L10" s="21" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="109.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="23" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="9" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="2" t="s">
+      <c r="B11" s="24" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="C11" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="D11" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="2" t="s">
+      <c r="F11" s="23">
+        <v>5</v>
+      </c>
+      <c r="G11" s="23">
+        <v>5</v>
+      </c>
+      <c r="H11" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="I11" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="J11" s="24" t="s">
+        <v>139</v>
+      </c>
+      <c r="K11" s="24" t="s">
+        <v>140</v>
+      </c>
+      <c r="L11" s="24" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="119.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="20" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="B12" s="21" t="s">
+        <v>142</v>
+      </c>
+      <c r="C12" s="20" t="s">
         <v>25</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="D12" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F10" s="4" t="s">
+      <c r="E12" s="20" t="s">
+        <v>16</v>
+      </c>
+      <c r="F12" s="20">
+        <v>2</v>
+      </c>
+      <c r="G12" s="20">
+        <v>2</v>
+      </c>
+      <c r="H12" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="I12" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="J12" s="21" t="s">
+        <v>143</v>
+      </c>
+      <c r="K12" s="21" t="s">
+        <v>144</v>
+      </c>
+      <c r="L12" s="21" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="117" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="23" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="2" t="s">
+      <c r="B13" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="C13" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="D13" s="24" t="s">
         <v>29</v>
       </c>
-      <c r="C11" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="E13" s="23" t="s">
+        <v>16</v>
+      </c>
+      <c r="F13" s="23">
+        <v>5</v>
+      </c>
+      <c r="G13" s="23">
+        <v>5</v>
+      </c>
+      <c r="H13" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="I13" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="J13" s="24" t="s">
+        <v>146</v>
+      </c>
+      <c r="K13" s="24" t="s">
+        <v>147</v>
+      </c>
+      <c r="L13" s="24" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A14" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
-        <v>31</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>34</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="B14" s="12"/>
-      <c r="C14" s="12"/>
-      <c r="D14" s="12"/>
-      <c r="E14" s="12"/>
-      <c r="F14" s="5" t="s">
-        <v>9</v>
-      </c>
+      <c r="B14" s="26"/>
+      <c r="C14" s="26"/>
+      <c r="D14" s="26"/>
+      <c r="E14" s="26"/>
+      <c r="F14" s="27">
+        <v>22</v>
+      </c>
+      <c r="G14" s="27">
+        <v>22</v>
+      </c>
+      <c r="H14" s="28"/>
+      <c r="I14" s="28"/>
+      <c r="J14" s="28"/>
+      <c r="K14" s="28"/>
+      <c r="L14" s="28"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="11">
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="H5:L5"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="H6:L6"/>
     <mergeCell ref="A14:E14"/>
+    <mergeCell ref="A1:L1"/>
+    <mergeCell ref="A2:L2"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="H3:L3"/>
     <mergeCell ref="B4:F4"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="H4:L4"/>
   </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
@@ -1115,193 +1476,193 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="16" t="s">
+      <c r="A1" s="8" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-      <c r="D1" s="12"/>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A2" s="6" t="s">
+      <c r="C4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D4" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B2" s="6" t="s">
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="B5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="D2" s="6" t="s">
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="B6" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D3" s="2" t="s">
+      <c r="C6" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="D6" s="5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4" s="8" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="9" t="s">
+      <c r="B7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="C4" s="9" t="s">
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="D4" s="9" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>49</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6" s="8" t="s">
-        <v>51</v>
-      </c>
-      <c r="B6" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>52</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A8" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="B8" s="9" t="s">
+      <c r="C11" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D11" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C8" s="9" t="s">
-        <v>57</v>
-      </c>
-      <c r="D8" s="9" t="s">
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
+      <c r="B12" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>57</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="C12" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="5" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A10" s="8" t="s">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="B10" s="9" t="s">
+      <c r="B13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C10" s="9" t="s">
-        <v>62</v>
-      </c>
-      <c r="D10" s="9" t="s">
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B14" s="5" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
+      <c r="C14" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="D14" s="5" t="s">
         <v>64</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="s">
-        <v>66</v>
-      </c>
-      <c r="B12" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D12" s="9" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>69</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="s">
-        <v>71</v>
-      </c>
-      <c r="B14" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="C14" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>73</v>
       </c>
     </row>
   </sheetData>
@@ -1323,186 +1684,186 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" ht="24" x14ac:dyDescent="0.25">
+      <c r="A3" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="12"/>
-      <c r="C1" s="12"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="10" t="s">
+      <c r="C5" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="B2" s="10" t="s">
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="B6" s="1" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="3" spans="1:3" ht="24" x14ac:dyDescent="0.25">
-      <c r="A3" s="8" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" s="9" t="s">
+      <c r="C6" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C3" s="9" t="s">
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>33</v>
-      </c>
-      <c r="B4" s="2" t="s">
+      <c r="B7" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C7" s="5" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="8" t="s">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="B5" s="9" t="s">
+      <c r="B8" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="C5" s="9" t="s">
+      <c r="C8" s="1" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
         <v>85</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B9" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C9" s="5" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="8" t="s">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B10" s="1" t="s">
         <v>89</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C10" s="1" t="s">
         <v>90</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
         <v>91</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B11" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C11" s="5" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="8" t="s">
+    <row r="12" spans="1:3" ht="24" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B9" s="9" t="s">
+      <c r="B12" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="C9" s="9" t="s">
+      <c r="C12" s="1" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B13" s="5" t="s">
         <v>98</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C13" s="5" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="8" t="s">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B11" s="9" t="s">
+      <c r="B14" s="1" t="s">
         <v>101</v>
       </c>
-      <c r="C11" s="9" t="s">
+      <c r="C14" s="1" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="12" spans="1:3" ht="24" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B15" s="5" t="s">
         <v>104</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C15" s="5" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="s">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="B13" s="9" t="s">
+      <c r="B16" s="1" t="s">
         <v>107</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C16" s="1" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B17" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C17" s="5" t="s">
         <v>111</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="s">
-        <v>112</v>
-      </c>
-      <c r="B15" s="9" t="s">
-        <v>113</v>
-      </c>
-      <c r="C15" s="9" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
-        <v>115</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="s">
-        <v>118</v>
-      </c>
-      <c r="B17" s="9" t="s">
-        <v>119</v>
-      </c>
-      <c r="C17" s="9" t="s">
-        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/Documentos Base/Sprint 4 documentacion/Sprint_04_Backlog_ICARO.xlsx
+++ b/Documentos Base/Sprint 4 documentacion/Sprint_04_Backlog_ICARO.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3043EBB9-4AC4-4DEF-83F9-D326ACE05761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Backlog Sprint 04" sheetId="4" r:id="rId1"/>
@@ -667,36 +667,9 @@
     <xf numFmtId="0" fontId="4" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="14" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -714,20 +687,47 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1042,424 +1042,424 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="24" t="s">
         <v>113</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-      <c r="G1" s="7"/>
-      <c r="H1" s="7"/>
-      <c r="I1" s="7"/>
-      <c r="J1" s="7"/>
-      <c r="K1" s="7"/>
-      <c r="L1" s="7"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
+      <c r="E1" s="25"/>
+      <c r="F1" s="25"/>
+      <c r="G1" s="25"/>
+      <c r="H1" s="25"/>
+      <c r="I1" s="25"/>
+      <c r="J1" s="25"/>
+      <c r="K1" s="25"/>
+      <c r="L1" s="25"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="26" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="7"/>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
+      <c r="B2" s="25"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="25"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="25"/>
+      <c r="G2" s="25"/>
+      <c r="H2" s="25"/>
+      <c r="I2" s="25"/>
+      <c r="J2" s="25"/>
+      <c r="K2" s="25"/>
+      <c r="L2" s="25"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="13" t="s">
+      <c r="B3" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="14"/>
-      <c r="D3" s="14"/>
-      <c r="E3" s="14"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="12" t="s">
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="H3" s="29">
+      <c r="H3" s="19">
         <v>4</v>
       </c>
-      <c r="I3" s="30"/>
-      <c r="J3" s="30"/>
-      <c r="K3" s="30"/>
-      <c r="L3" s="31"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
+      <c r="L3" s="21"/>
     </row>
     <row r="4" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A4" s="12" t="s">
+      <c r="A4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="16">
+      <c r="B4" s="27">
         <v>46116</v>
       </c>
-      <c r="C4" s="17"/>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17"/>
-      <c r="F4" s="18"/>
-      <c r="G4" s="12" t="s">
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="28"/>
+      <c r="F4" s="29"/>
+      <c r="G4" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="H4" s="16">
+      <c r="H4" s="27">
         <v>46150</v>
       </c>
-      <c r="I4" s="17"/>
-      <c r="J4" s="17"/>
-      <c r="K4" s="17"/>
-      <c r="L4" s="18"/>
+      <c r="I4" s="28"/>
+      <c r="J4" s="28"/>
+      <c r="K4" s="28"/>
+      <c r="L4" s="29"/>
     </row>
     <row r="5" spans="1:12" ht="95.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="12" t="s">
+      <c r="A5" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="13" t="s">
+      <c r="B5" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14"/>
-      <c r="E5" s="14"/>
-      <c r="F5" s="15"/>
-      <c r="G5" s="12" t="s">
+      <c r="C5" s="17"/>
+      <c r="D5" s="17"/>
+      <c r="E5" s="17"/>
+      <c r="F5" s="18"/>
+      <c r="G5" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="H5" s="13" t="s">
+      <c r="H5" s="16" t="s">
         <v>118</v>
       </c>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14"/>
-      <c r="K5" s="14"/>
-      <c r="L5" s="15"/>
+      <c r="I5" s="17"/>
+      <c r="J5" s="17"/>
+      <c r="K5" s="17"/>
+      <c r="L5" s="18"/>
     </row>
     <row r="6" spans="1:12" ht="24" x14ac:dyDescent="0.25">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="29">
+      <c r="B6" s="19">
         <v>22</v>
       </c>
-      <c r="C6" s="30"/>
-      <c r="D6" s="30"/>
-      <c r="E6" s="30"/>
-      <c r="F6" s="31"/>
-      <c r="G6" s="12" t="s">
+      <c r="C6" s="20"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="20"/>
+      <c r="F6" s="21"/>
+      <c r="G6" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="H6" s="13" t="s">
+      <c r="H6" s="16" t="s">
         <v>120</v>
       </c>
-      <c r="I6" s="14"/>
-      <c r="J6" s="14"/>
-      <c r="K6" s="14"/>
-      <c r="L6" s="15"/>
+      <c r="I6" s="17"/>
+      <c r="J6" s="17"/>
+      <c r="K6" s="17"/>
+      <c r="L6" s="18"/>
     </row>
     <row r="7" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="19" t="s">
+      <c r="A7" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="19" t="s">
+      <c r="B7" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C7" s="19" t="s">
+      <c r="C7" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="8" t="s">
         <v>11</v>
       </c>
-      <c r="G7" s="19" t="s">
+      <c r="G7" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="H7" s="19" t="s">
+      <c r="H7" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="I7" s="19" t="s">
+      <c r="I7" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="J7" s="19" t="s">
+      <c r="J7" s="8" t="s">
         <v>128</v>
       </c>
-      <c r="K7" s="19" t="s">
+      <c r="K7" s="8" t="s">
         <v>124</v>
       </c>
-      <c r="L7" s="19" t="s">
+      <c r="L7" s="8" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="126.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="20" t="s">
+      <c r="A8" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D8" s="21" t="s">
+      <c r="D8" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F8" s="20">
+      <c r="F8" s="9">
         <v>5</v>
       </c>
-      <c r="G8" s="20">
+      <c r="G8" s="9">
         <v>5</v>
       </c>
-      <c r="H8" s="21" t="s">
+      <c r="H8" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="I8" s="22" t="s">
+      <c r="I8" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="J8" s="21" t="s">
+      <c r="J8" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="K8" s="21" t="s">
+      <c r="K8" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="L8" s="21" t="s">
+      <c r="L8" s="10" t="s">
         <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="B9" s="24" t="s">
+      <c r="B9" s="13" t="s">
         <v>132</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D9" s="24" t="s">
+      <c r="D9" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E9" s="23" t="s">
+      <c r="E9" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="23">
+      <c r="F9" s="12">
         <v>3</v>
       </c>
-      <c r="G9" s="23">
+      <c r="G9" s="12">
         <v>3</v>
       </c>
-      <c r="H9" s="21" t="s">
+      <c r="H9" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="I9" s="22" t="s">
+      <c r="I9" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="J9" s="24" t="s">
+      <c r="J9" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="K9" s="24" t="s">
+      <c r="K9" s="13" t="s">
         <v>134</v>
       </c>
-      <c r="L9" s="24" t="s">
+      <c r="L9" s="13" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="120.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="20" t="s">
+      <c r="A10" s="9" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="20" t="s">
+      <c r="C10" s="9" t="s">
         <v>14</v>
       </c>
-      <c r="D10" s="21" t="s">
+      <c r="D10" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="E10" s="20" t="s">
+      <c r="E10" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F10" s="20">
+      <c r="F10" s="9">
         <v>2</v>
       </c>
-      <c r="G10" s="20">
+      <c r="G10" s="9">
         <v>2</v>
       </c>
-      <c r="H10" s="21" t="s">
+      <c r="H10" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="I10" s="22" t="s">
+      <c r="I10" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="J10" s="21" t="s">
+      <c r="J10" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="K10" s="21" t="s">
+      <c r="K10" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="L10" s="21" t="s">
+      <c r="L10" s="10" t="s">
         <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="109.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="B11" s="24" t="s">
+      <c r="B11" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="D11" s="24" t="s">
+      <c r="D11" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="E11" s="23" t="s">
+      <c r="E11" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="F11" s="23">
+      <c r="F11" s="12">
         <v>5</v>
       </c>
-      <c r="G11" s="23">
+      <c r="G11" s="12">
         <v>5</v>
       </c>
-      <c r="H11" s="21" t="s">
+      <c r="H11" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="I11" s="22" t="s">
+      <c r="I11" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="J11" s="24" t="s">
+      <c r="J11" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="K11" s="24" t="s">
+      <c r="K11" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="L11" s="24" t="s">
+      <c r="L11" s="13" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="119.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="C12" s="20" t="s">
+      <c r="C12" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="D12" s="21" t="s">
+      <c r="D12" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="E12" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="20">
+      <c r="F12" s="9">
         <v>2</v>
       </c>
-      <c r="G12" s="20">
+      <c r="G12" s="9">
         <v>2</v>
       </c>
-      <c r="H12" s="21" t="s">
+      <c r="H12" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="I12" s="22" t="s">
+      <c r="I12" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="J12" s="21" t="s">
+      <c r="J12" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="K12" s="21" t="s">
+      <c r="K12" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="L12" s="21" t="s">
+      <c r="L12" s="10" t="s">
         <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="117" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="23" t="s">
+      <c r="A13" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B13" s="24" t="s">
+      <c r="B13" s="13" t="s">
         <v>28</v>
       </c>
-      <c r="C13" s="23" t="s">
+      <c r="C13" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="D13" s="24" t="s">
+      <c r="D13" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="E13" s="23" t="s">
+      <c r="E13" s="12" t="s">
         <v>16</v>
       </c>
-      <c r="F13" s="23">
+      <c r="F13" s="12">
         <v>5</v>
       </c>
-      <c r="G13" s="23">
+      <c r="G13" s="12">
         <v>5</v>
       </c>
-      <c r="H13" s="21" t="s">
+      <c r="H13" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="I13" s="22" t="s">
+      <c r="I13" s="11" t="s">
         <v>127</v>
       </c>
-      <c r="J13" s="24" t="s">
+      <c r="J13" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="K13" s="24" t="s">
+      <c r="K13" s="13" t="s">
         <v>147</v>
       </c>
-      <c r="L13" s="24" t="s">
+      <c r="L13" s="13" t="s">
         <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="25" t="s">
+      <c r="A14" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="26"/>
-      <c r="C14" s="26"/>
-      <c r="D14" s="26"/>
-      <c r="E14" s="26"/>
-      <c r="F14" s="27">
+      <c r="B14" s="23"/>
+      <c r="C14" s="23"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="23"/>
+      <c r="F14" s="15">
         <v>22</v>
       </c>
-      <c r="G14" s="27">
+      <c r="G14" s="15">
         <v>22</v>
       </c>
-      <c r="H14" s="28"/>
-      <c r="I14" s="28"/>
-      <c r="J14" s="28"/>
-      <c r="K14" s="28"/>
-      <c r="L14" s="28"/>
+      <c r="H14" s="14"/>
+      <c r="I14" s="14"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="H5:L5"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="H6:L6"/>
-    <mergeCell ref="A14:E14"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="H4:L4"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="H5:L5"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="A14:E14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1476,12 +1476,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
-      <c r="D1" s="7"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
+      <c r="D1" s="25"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -1684,11 +1684,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="7"/>
-      <c r="C1" s="7"/>
+      <c r="B1" s="25"/>
+      <c r="C1" s="25"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">

--- a/Documentos Base/Sprint 4 documentacion/Sprint_04_Backlog_ICARO.xlsx
+++ b/Documentos Base/Sprint 4 documentacion/Sprint_04_Backlog_ICARO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Desktop\Sistema_Gestion_Integral_Constructora\Documentos Base\Sprint 4 documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3043EBB9-4AC4-4DEF-83F9-D326ACE05761}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F988439-E337-4CEA-BE67-59FBA71F500F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Backlog Sprint 04" sheetId="4" r:id="rId1"/>
@@ -363,9 +363,6 @@
     <t>Compromisos Sprint 03 8.3 cum.</t>
   </si>
   <si>
-    <t>SPRINT BACKLOG — Sprint 03: Catalogo de Materiales, Gestion de Bodega e Inventario</t>
-  </si>
-  <si>
     <t>ICARO CONSTRUCTORES BMGM S.A.S.  |  Sistema de Gestion Integral de Obra</t>
   </si>
   <si>
@@ -472,6 +469,9 @@
   </si>
   <si>
     <t>Implementar el módulo de Requerimientos de Compra con CRUD completo, registro de líneas de detalle, consulta por proyecto, filtros operativos, flujo de aprobación y rechazo con control RBAC, validación de justificación obligatoria para rechazos y formalización del endpoint de reactivación de materiales dados de baja. Adicionalmente, ampliar la cobertura de pruebas automatizadas sobre requerimientos de compra, aprobación/rechazo y reactivación de materiales</t>
+  </si>
+  <si>
+    <t>SPRINT BACKLOG — Sprint 04</t>
   </si>
 </sst>
 </file>
@@ -1043,7 +1043,7 @@
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" x14ac:dyDescent="0.25">
       <c r="A1" s="24" t="s">
-        <v>113</v>
+        <v>149</v>
       </c>
       <c r="B1" s="25"/>
       <c r="C1" s="25"/>
@@ -1059,7 +1059,7 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="26" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B2" s="25"/>
       <c r="C2" s="25"/>
@@ -1085,7 +1085,7 @@
       <c r="E3" s="17"/>
       <c r="F3" s="18"/>
       <c r="G3" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="H3" s="19">
         <v>4</v>
@@ -1107,7 +1107,7 @@
       <c r="E4" s="28"/>
       <c r="F4" s="29"/>
       <c r="G4" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="H4" s="27">
         <v>46150</v>
@@ -1122,17 +1122,17 @@
         <v>3</v>
       </c>
       <c r="B5" s="16" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C5" s="17"/>
       <c r="D5" s="17"/>
       <c r="E5" s="17"/>
       <c r="F5" s="18"/>
       <c r="G5" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="H5" s="16" t="s">
         <v>117</v>
-      </c>
-      <c r="H5" s="16" t="s">
-        <v>118</v>
       </c>
       <c r="I5" s="17"/>
       <c r="J5" s="17"/>
@@ -1151,10 +1151,10 @@
       <c r="E6" s="20"/>
       <c r="F6" s="21"/>
       <c r="G6" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="H6" s="16" t="s">
         <v>119</v>
-      </c>
-      <c r="H6" s="16" t="s">
-        <v>120</v>
       </c>
       <c r="I6" s="17"/>
       <c r="J6" s="17"/>
@@ -1181,22 +1181,22 @@
         <v>11</v>
       </c>
       <c r="G7" s="8" t="s">
+        <v>120</v>
+      </c>
+      <c r="H7" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="H7" s="8" t="s">
+      <c r="I7" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="I7" s="8" t="s">
+      <c r="J7" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="K7" s="8" t="s">
         <v>123</v>
       </c>
-      <c r="J7" s="8" t="s">
-        <v>128</v>
-      </c>
-      <c r="K7" s="8" t="s">
+      <c r="L7" s="8" t="s">
         <v>124</v>
-      </c>
-      <c r="L7" s="8" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="126.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1222,19 +1222,19 @@
         <v>5</v>
       </c>
       <c r="H8" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="I8" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="I8" s="11" t="s">
-        <v>127</v>
-      </c>
       <c r="J8" s="10" t="s">
+        <v>128</v>
+      </c>
+      <c r="K8" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="K8" s="10" t="s">
+      <c r="L8" s="10" t="s">
         <v>130</v>
-      </c>
-      <c r="L8" s="10" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="96.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1242,7 +1242,7 @@
         <v>17</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C9" s="12" t="s">
         <v>14</v>
@@ -1260,19 +1260,19 @@
         <v>3</v>
       </c>
       <c r="H9" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="I9" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="I9" s="11" t="s">
-        <v>127</v>
-      </c>
       <c r="J9" s="13" t="s">
+        <v>132</v>
+      </c>
+      <c r="K9" s="13" t="s">
         <v>133</v>
       </c>
-      <c r="K9" s="13" t="s">
+      <c r="L9" s="13" t="s">
         <v>134</v>
-      </c>
-      <c r="L9" s="13" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="120.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1298,19 +1298,19 @@
         <v>2</v>
       </c>
       <c r="H10" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="I10" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="I10" s="11" t="s">
-        <v>127</v>
-      </c>
       <c r="J10" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="K10" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="K10" s="10" t="s">
+      <c r="L10" s="10" t="s">
         <v>137</v>
-      </c>
-      <c r="L10" s="10" t="s">
-        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="109.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -1336,19 +1336,19 @@
         <v>5</v>
       </c>
       <c r="H11" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="I11" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="I11" s="11" t="s">
-        <v>127</v>
-      </c>
       <c r="J11" s="13" t="s">
+        <v>138</v>
+      </c>
+      <c r="K11" s="13" t="s">
         <v>139</v>
       </c>
-      <c r="K11" s="13" t="s">
+      <c r="L11" s="13" t="s">
         <v>140</v>
-      </c>
-      <c r="L11" s="13" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="119.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -1356,7 +1356,7 @@
         <v>24</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C12" s="9" t="s">
         <v>25</v>
@@ -1374,19 +1374,19 @@
         <v>2</v>
       </c>
       <c r="H12" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="I12" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="I12" s="11" t="s">
-        <v>127</v>
-      </c>
       <c r="J12" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="K12" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="K12" s="10" t="s">
+      <c r="L12" s="10" t="s">
         <v>144</v>
-      </c>
-      <c r="L12" s="10" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="117" customHeight="1" x14ac:dyDescent="0.25">
@@ -1412,19 +1412,19 @@
         <v>5</v>
       </c>
       <c r="H13" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="I13" s="11" t="s">
         <v>126</v>
       </c>
-      <c r="I13" s="11" t="s">
-        <v>127</v>
-      </c>
       <c r="J13" s="13" t="s">
+        <v>145</v>
+      </c>
+      <c r="K13" s="13" t="s">
         <v>146</v>
       </c>
-      <c r="K13" s="13" t="s">
+      <c r="L13" s="13" t="s">
         <v>147</v>
-      </c>
-      <c r="L13" s="13" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">

--- a/Documentos Base/Sprint 4 documentacion/Sprint_04_Backlog_ICARO.xlsx
+++ b/Documentos Base/Sprint 4 documentacion/Sprint_04_Backlog_ICARO.xlsx
@@ -8,21 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Desktop\Sistema_Gestion_Integral_Constructora\Documentos Base\Sprint 4 documentacion\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6F988439-E337-4CEA-BE67-59FBA71F500F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5444F259-F2CE-4F87-A81F-2A9207556B14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Backlog Sprint 04" sheetId="4" r:id="rId1"/>
     <sheet name="Resumen Velocidad" sheetId="2" r:id="rId2"/>
     <sheet name="Glosario" sheetId="3" r:id="rId3"/>
+    <sheet name="Resumen Casos de prueba " sheetId="5" r:id="rId4"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="216">
   <si>
     <t>ICARO CONSTRUCTORES BMGM S.A.S.</t>
   </si>
@@ -472,13 +473,211 @@
   </si>
   <si>
     <t>SPRINT BACKLOG — Sprint 04</t>
+  </si>
+  <si>
+    <t>ID CP</t>
+  </si>
+  <si>
+    <t>Grupo</t>
+  </si>
+  <si>
+    <t>Descripción</t>
+  </si>
+  <si>
+    <t>Evidencia</t>
+  </si>
+  <si>
+    <t>Grupo 1</t>
+  </si>
+  <si>
+    <t>Catálogo de Materiales</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>Grupo 2</t>
+  </si>
+  <si>
+    <t>Grupo 3</t>
+  </si>
+  <si>
+    <t>Requerimientos de Compra</t>
+  </si>
+  <si>
+    <t>POST /compras/proyectos/:id/requerimientos sin token → 401 Unauthorized</t>
+  </si>
+  <si>
+    <t>POST .../requerimientos con Contador → 403 Forbidden</t>
+  </si>
+  <si>
+    <t>POST .../requerimientos con Admin + body completo → pasa RBAC</t>
+  </si>
+  <si>
+    <t>Aprobación/Rechazo</t>
+  </si>
+  <si>
+    <t>PUT /compras/requerimientos/:id/aprobar sin token → 401 Unauthorized</t>
+  </si>
+  <si>
+    <t>PUT .../aprobar con Residente → 403 Forbidden</t>
+  </si>
+  <si>
+    <t>CP-051</t>
+  </si>
+  <si>
+    <t>compras_requerimientos.test.js – Test 01</t>
+  </si>
+  <si>
+    <t>CP-052</t>
+  </si>
+  <si>
+    <t>compras_requerimientos.test.js – Test 02</t>
+  </si>
+  <si>
+    <t>CP-053</t>
+  </si>
+  <si>
+    <t>POST .../requerimientos con Residente sin detalles → pasa RBAC y valida campos</t>
+  </si>
+  <si>
+    <t>compras_requerimientos.test.js – Test 03</t>
+  </si>
+  <si>
+    <t>CP-054</t>
+  </si>
+  <si>
+    <t>compras_requerimientos.test.js – Test 04</t>
+  </si>
+  <si>
+    <t>CP-055</t>
+  </si>
+  <si>
+    <t>GET /compras/proyectos/:id/requerimientos sin token → 401 Unauthorized</t>
+  </si>
+  <si>
+    <t>compras_requerimientos.test.js – Test 05</t>
+  </si>
+  <si>
+    <t>CP-056</t>
+  </si>
+  <si>
+    <t>GET .../requerimientos con Admin → pasa autenticación y RBAC</t>
+  </si>
+  <si>
+    <t>compras_requerimientos.test.js – Test 06</t>
+  </si>
+  <si>
+    <t>CP-057</t>
+  </si>
+  <si>
+    <t>GET .../requerimientos con Bodeguero → pasa autenticación para lectura</t>
+  </si>
+  <si>
+    <t>compras_requerimientos.test.js – Test 07</t>
+  </si>
+  <si>
+    <t>CP-058</t>
+  </si>
+  <si>
+    <t>GET /compras/requerimientos/:id con Contador → pasa autenticación para lectura</t>
+  </si>
+  <si>
+    <t>compras_requerimientos.test.js – Test 08</t>
+  </si>
+  <si>
+    <t>CP-059</t>
+  </si>
+  <si>
+    <t>compras_requerimientos.test.js – Test 09</t>
+  </si>
+  <si>
+    <t>CP-060</t>
+  </si>
+  <si>
+    <t>compras_requerimientos.test.js – Test 10</t>
+  </si>
+  <si>
+    <t>CP-061</t>
+  </si>
+  <si>
+    <t>PUT .../aprobar con Admin → pasa RBAC</t>
+  </si>
+  <si>
+    <t>compras_requerimientos.test.js – Test 11</t>
+  </si>
+  <si>
+    <t>CP-062</t>
+  </si>
+  <si>
+    <t>PUT /compras/requerimientos/:id/rechazar sin token → 401 Unauthorized</t>
+  </si>
+  <si>
+    <t>compras_requerimientos.test.js – Test 12</t>
+  </si>
+  <si>
+    <t>CP-063</t>
+  </si>
+  <si>
+    <t>PUT .../rechazar con Residente → 403 Forbidden</t>
+  </si>
+  <si>
+    <t>compras_requerimientos.test.js – Test 13</t>
+  </si>
+  <si>
+    <t>CP-064</t>
+  </si>
+  <si>
+    <t>PUT .../rechazar con Admin sin comentarioRechazo → valida comentario obligatorio</t>
+  </si>
+  <si>
+    <t>compras_requerimientos.test.js – Test 14</t>
+  </si>
+  <si>
+    <t>CP-065</t>
+  </si>
+  <si>
+    <t>PUT /materiales/:id sin token → 401 Unauthorized</t>
+  </si>
+  <si>
+    <t>compras_requerimientos.test.js – Test 15</t>
+  </si>
+  <si>
+    <t>CP-066</t>
+  </si>
+  <si>
+    <t>PUT /materiales/:id con Residente → 403 Forbidden</t>
+  </si>
+  <si>
+    <t>compras_requerimientos.test.js – Test 16</t>
+  </si>
+  <si>
+    <t>CP-067</t>
+  </si>
+  <si>
+    <t>PUT /materiales/:id con Admin y { activo: true } → pasa RBAC y reactiva material</t>
+  </si>
+  <si>
+    <t>compras_requerimientos.test.js – Test 17</t>
+  </si>
+  <si>
+    <t>CP-068</t>
+  </si>
+  <si>
+    <t>GET /materiales?soloActivos=false con Admin → catálogo completo incluyendo inactivos</t>
+  </si>
+  <si>
+    <t>compras_requerimientos.test.js – Test 18</t>
+  </si>
+  <si>
+    <t>RESUMEN DE CASOS DE PRUEBA — SPRINT 04 (CP-051 a CP-068)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -491,59 +690,91 @@
       <sz val="13"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF1F3864"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <i/>
       <sz val="9"/>
       <color rgb="FF595959"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF1F3864"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="8">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -580,8 +811,20 @@
         <fgColor rgb="FFE2EFDA"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.59999389629810485"/>
+        <bgColor indexed="65"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="5">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -643,11 +886,73 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -691,6 +996,16 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -702,37 +1017,222 @@
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="40% - Énfasis3" xfId="1" builtinId="39"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="0"/>
+  <dxfs count="11">
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right/>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left/>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top style="thin">
+          <color auto="1"/>
+        </top>
+        <bottom style="thin">
+          <color auto="1"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="3"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="thin">
+          <color auto="1"/>
+        </left>
+        <right style="thin">
+          <color auto="1"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -743,6 +1243,21 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{5E947C2E-CEC8-49E2-A9F6-3CDC88181669}" name="Tabla1" displayName="Tabla1" ref="A2:F20" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" headerRowBorderDxfId="7" tableBorderDxfId="8" totalsRowBorderDxfId="6">
+  <autoFilter ref="A2:F20" xr:uid="{5E947C2E-CEC8-49E2-A9F6-3CDC88181669}"/>
+  <tableColumns count="6">
+    <tableColumn id="1" xr3:uid="{36341BDF-7A51-46C5-9710-6CD059DBD4C1}" name="ID CP" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{4CB28B24-B22B-4DF2-AB02-083D061E4475}" name="Grupo" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{307F7102-A9AA-424B-BBDD-BFD3F56C804E}" name="Módulo" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{493DEC0E-721B-4E02-8BA8-8A722D15F928}" name="Descripción" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{6036B6FA-3A36-4F19-8066-7F763B713B83}" name="Estado" dataDxfId="1" dataCellStyle="40% - Énfasis3"/>
+    <tableColumn id="6" xr3:uid="{F9AF1C15-D30B-42F2-9620-1F78ACDB0EA6}" name="Evidencia" dataDxfId="0"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1034,132 +1549,133 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="34.5703125" customWidth="1"/>
-    <col min="6" max="6" width="9.5703125" customWidth="1"/>
-    <col min="8" max="8" width="20.7109375" customWidth="1"/>
-    <col min="10" max="10" width="48.42578125" customWidth="1"/>
+    <col min="5" max="5" width="15.42578125" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" customWidth="1"/>
+    <col min="8" max="8" width="26" customWidth="1"/>
+    <col min="10" max="10" width="54.42578125" customWidth="1"/>
     <col min="11" max="11" width="25.85546875" customWidth="1"/>
     <col min="12" max="12" width="44.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A1" s="24" t="s">
+      <c r="A1" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="19" t="s">
         <v>113</v>
       </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
-      <c r="L2" s="25"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="18"/>
+      <c r="C3" s="21"/>
+      <c r="D3" s="21"/>
+      <c r="E3" s="21"/>
+      <c r="F3" s="22"/>
       <c r="G3" s="7" t="s">
         <v>114</v>
       </c>
-      <c r="H3" s="19">
+      <c r="H3" s="23">
         <v>4</v>
       </c>
-      <c r="I3" s="20"/>
-      <c r="J3" s="20"/>
-      <c r="K3" s="20"/>
-      <c r="L3" s="21"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="25"/>
     </row>
     <row r="4" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="27">
+      <c r="B4" s="26">
         <v>46116</v>
       </c>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="28"/>
-      <c r="F4" s="29"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="27"/>
+      <c r="E4" s="27"/>
+      <c r="F4" s="28"/>
       <c r="G4" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="H4" s="27">
+      <c r="H4" s="26">
         <v>46150</v>
       </c>
-      <c r="I4" s="28"/>
-      <c r="J4" s="28"/>
-      <c r="K4" s="28"/>
-      <c r="L4" s="29"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="27"/>
+      <c r="K4" s="27"/>
+      <c r="L4" s="28"/>
     </row>
     <row r="5" spans="1:12" ht="95.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="16" t="s">
+      <c r="B5" s="20" t="s">
         <v>148</v>
       </c>
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="17"/>
-      <c r="F5" s="18"/>
+      <c r="C5" s="21"/>
+      <c r="D5" s="21"/>
+      <c r="E5" s="21"/>
+      <c r="F5" s="22"/>
       <c r="G5" s="7" t="s">
         <v>116</v>
       </c>
-      <c r="H5" s="16" t="s">
+      <c r="H5" s="20" t="s">
         <v>117</v>
       </c>
-      <c r="I5" s="17"/>
-      <c r="J5" s="17"/>
-      <c r="K5" s="17"/>
-      <c r="L5" s="18"/>
+      <c r="I5" s="21"/>
+      <c r="J5" s="21"/>
+      <c r="K5" s="21"/>
+      <c r="L5" s="22"/>
     </row>
     <row r="6" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="19">
+      <c r="B6" s="23">
         <v>22</v>
       </c>
-      <c r="C6" s="20"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="20"/>
-      <c r="F6" s="21"/>
+      <c r="C6" s="24"/>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="25"/>
       <c r="G6" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="H6" s="16" t="s">
+      <c r="H6" s="20" t="s">
         <v>119</v>
       </c>
-      <c r="I6" s="17"/>
-      <c r="J6" s="17"/>
-      <c r="K6" s="17"/>
-      <c r="L6" s="18"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="21"/>
+      <c r="K6" s="21"/>
+      <c r="L6" s="22"/>
     </row>
     <row r="7" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
@@ -1428,13 +1944,13 @@
       </c>
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="22" t="s">
+      <c r="A14" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="B14" s="23"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="30"/>
+      <c r="D14" s="30"/>
+      <c r="E14" s="30"/>
       <c r="F14" s="15">
         <v>22</v>
       </c>
@@ -1449,17 +1965,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="H5:L5"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="H6:L6"/>
+    <mergeCell ref="A14:E14"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="H3:L3"/>
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="H4:L4"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="H5:L5"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="H6:L6"/>
-    <mergeCell ref="A14:E14"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1476,12 +1992,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="30" t="s">
+      <c r="A1" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
-      <c r="D1" s="25"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
@@ -1684,11 +2200,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="31" t="s">
+      <c r="A1" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="25"/>
-      <c r="C1" s="25"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="6" t="s">
@@ -1872,4 +2388,415 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85D58317-324F-46CD-9C52-7BBEDC1AB341}">
+  <dimension ref="A1:F20"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="28.5703125" customWidth="1"/>
+    <col min="4" max="4" width="78.42578125" customWidth="1"/>
+    <col min="6" max="6" width="39.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A1" s="32" t="s">
+        <v>215</v>
+      </c>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="B2" s="34" t="s">
+        <v>151</v>
+      </c>
+      <c r="C2" s="34" t="s">
+        <v>9</v>
+      </c>
+      <c r="D2" s="34" t="s">
+        <v>152</v>
+      </c>
+      <c r="E2" s="34" t="s">
+        <v>122</v>
+      </c>
+      <c r="F2" s="35" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" s="36" t="s">
+        <v>166</v>
+      </c>
+      <c r="B3" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="C3" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="D3" s="38" t="s">
+        <v>160</v>
+      </c>
+      <c r="E3" s="39" t="s">
+        <v>156</v>
+      </c>
+      <c r="F3" s="40" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" s="36" t="s">
+        <v>168</v>
+      </c>
+      <c r="B4" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="C4" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="D4" s="38" t="s">
+        <v>161</v>
+      </c>
+      <c r="E4" s="39" t="s">
+        <v>156</v>
+      </c>
+      <c r="F4" s="40" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" s="36" t="s">
+        <v>170</v>
+      </c>
+      <c r="B5" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="C5" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="D5" s="38" t="s">
+        <v>171</v>
+      </c>
+      <c r="E5" s="39" t="s">
+        <v>156</v>
+      </c>
+      <c r="F5" s="40" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" s="36" t="s">
+        <v>173</v>
+      </c>
+      <c r="B6" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="C6" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="D6" s="38" t="s">
+        <v>162</v>
+      </c>
+      <c r="E6" s="39" t="s">
+        <v>156</v>
+      </c>
+      <c r="F6" s="40" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" s="36" t="s">
+        <v>175</v>
+      </c>
+      <c r="B7" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="C7" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="D7" s="38" t="s">
+        <v>176</v>
+      </c>
+      <c r="E7" s="39" t="s">
+        <v>156</v>
+      </c>
+      <c r="F7" s="40" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" s="36" t="s">
+        <v>178</v>
+      </c>
+      <c r="B8" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="C8" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="D8" s="38" t="s">
+        <v>179</v>
+      </c>
+      <c r="E8" s="39" t="s">
+        <v>156</v>
+      </c>
+      <c r="F8" s="40" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" s="36" t="s">
+        <v>181</v>
+      </c>
+      <c r="B9" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="C9" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="D9" s="38" t="s">
+        <v>182</v>
+      </c>
+      <c r="E9" s="39" t="s">
+        <v>156</v>
+      </c>
+      <c r="F9" s="40" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" s="36" t="s">
+        <v>184</v>
+      </c>
+      <c r="B10" s="37" t="s">
+        <v>154</v>
+      </c>
+      <c r="C10" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="D10" s="38" t="s">
+        <v>185</v>
+      </c>
+      <c r="E10" s="39" t="s">
+        <v>156</v>
+      </c>
+      <c r="F10" s="40" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="36" t="s">
+        <v>187</v>
+      </c>
+      <c r="B11" s="37" t="s">
+        <v>157</v>
+      </c>
+      <c r="C11" s="37" t="s">
+        <v>163</v>
+      </c>
+      <c r="D11" s="38" t="s">
+        <v>164</v>
+      </c>
+      <c r="E11" s="39" t="s">
+        <v>156</v>
+      </c>
+      <c r="F11" s="40" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" s="36" t="s">
+        <v>189</v>
+      </c>
+      <c r="B12" s="37" t="s">
+        <v>157</v>
+      </c>
+      <c r="C12" s="37" t="s">
+        <v>163</v>
+      </c>
+      <c r="D12" s="38" t="s">
+        <v>165</v>
+      </c>
+      <c r="E12" s="39" t="s">
+        <v>156</v>
+      </c>
+      <c r="F12" s="40" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="36" t="s">
+        <v>191</v>
+      </c>
+      <c r="B13" s="37" t="s">
+        <v>157</v>
+      </c>
+      <c r="C13" s="37" t="s">
+        <v>163</v>
+      </c>
+      <c r="D13" s="38" t="s">
+        <v>192</v>
+      </c>
+      <c r="E13" s="39" t="s">
+        <v>156</v>
+      </c>
+      <c r="F13" s="40" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="36" t="s">
+        <v>194</v>
+      </c>
+      <c r="B14" s="37" t="s">
+        <v>157</v>
+      </c>
+      <c r="C14" s="37" t="s">
+        <v>163</v>
+      </c>
+      <c r="D14" s="38" t="s">
+        <v>195</v>
+      </c>
+      <c r="E14" s="39" t="s">
+        <v>156</v>
+      </c>
+      <c r="F14" s="40" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="36" t="s">
+        <v>197</v>
+      </c>
+      <c r="B15" s="37" t="s">
+        <v>157</v>
+      </c>
+      <c r="C15" s="37" t="s">
+        <v>163</v>
+      </c>
+      <c r="D15" s="38" t="s">
+        <v>198</v>
+      </c>
+      <c r="E15" s="39" t="s">
+        <v>156</v>
+      </c>
+      <c r="F15" s="40" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="36" t="s">
+        <v>200</v>
+      </c>
+      <c r="B16" s="37" t="s">
+        <v>157</v>
+      </c>
+      <c r="C16" s="37" t="s">
+        <v>163</v>
+      </c>
+      <c r="D16" s="38" t="s">
+        <v>201</v>
+      </c>
+      <c r="E16" s="39" t="s">
+        <v>156</v>
+      </c>
+      <c r="F16" s="40" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="36" t="s">
+        <v>203</v>
+      </c>
+      <c r="B17" s="37" t="s">
+        <v>158</v>
+      </c>
+      <c r="C17" s="37" t="s">
+        <v>155</v>
+      </c>
+      <c r="D17" s="38" t="s">
+        <v>204</v>
+      </c>
+      <c r="E17" s="39" t="s">
+        <v>156</v>
+      </c>
+      <c r="F17" s="40" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" s="36" t="s">
+        <v>206</v>
+      </c>
+      <c r="B18" s="37" t="s">
+        <v>158</v>
+      </c>
+      <c r="C18" s="37" t="s">
+        <v>155</v>
+      </c>
+      <c r="D18" s="38" t="s">
+        <v>207</v>
+      </c>
+      <c r="E18" s="39" t="s">
+        <v>156</v>
+      </c>
+      <c r="F18" s="40" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="36" t="s">
+        <v>209</v>
+      </c>
+      <c r="B19" s="37" t="s">
+        <v>158</v>
+      </c>
+      <c r="C19" s="37" t="s">
+        <v>155</v>
+      </c>
+      <c r="D19" s="38" t="s">
+        <v>210</v>
+      </c>
+      <c r="E19" s="39" t="s">
+        <v>156</v>
+      </c>
+      <c r="F19" s="40" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20" s="36" t="s">
+        <v>212</v>
+      </c>
+      <c r="B20" s="37" t="s">
+        <v>158</v>
+      </c>
+      <c r="C20" s="37" t="s">
+        <v>155</v>
+      </c>
+      <c r="D20" s="38" t="s">
+        <v>213</v>
+      </c>
+      <c r="E20" s="39" t="s">
+        <v>156</v>
+      </c>
+      <c r="F20" s="40" t="s">
+        <v>214</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>